--- a/BeatnotePostCombFix/Apr22,2026/April22Data.xlsx
+++ b/BeatnotePostCombFix/Apr22,2026/April22Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostCombFix\Apr22,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostCombFix\Apr22,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB52344-90A4-4FAA-9C5F-6CBB88194937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80EFFB8-EEDC-4A03-9B70-580FC4BAD565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="456" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -651,6 +648,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -658,7 +656,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -748,11 +745,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'456'!$G$1</c:f>
+              <c:f>'456'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>T</c:v>
+                  <c:v>mv</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -781,111 +778,111 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>'456'!$G$2:$G$35</c:f>
+              <c:f>'456'!$F$2:$F$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="34"/>
                 <c:pt idx="0">
-                  <c:v>44.616479827190098</c:v>
+                  <c:v>2.6128900409344502</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.608985675891397</c:v>
+                  <c:v>2.36107983882557</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44.633982113592403</c:v>
+                  <c:v>2.1040633860176099</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>44.518203405015498</c:v>
+                  <c:v>2.8591168018311102</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44.571552788051399</c:v>
+                  <c:v>2.6133130577580999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40.581290018634199</c:v>
+                  <c:v>2.6008104594610799</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>44.560706422052597</c:v>
+                  <c:v>2.6064494052098901</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>41.480349265655903</c:v>
+                  <c:v>2.60903369803468</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>44.5931305703091</c:v>
+                  <c:v>2.3638618219060099</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>40.603145527164401</c:v>
+                  <c:v>2.3678214034831799</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>40.605749735184801</c:v>
+                  <c:v>2.6142636356787401</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>44.594669571274103</c:v>
+                  <c:v>2.6162164987482401</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>44.757313156649801</c:v>
+                  <c:v>2.1075436068675701</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>40.7530404969201</c:v>
+                  <c:v>2.3875663779310199</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>40.754031808700198</c:v>
+                  <c:v>2.1022171308264399</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>40.733900497664997</c:v>
+                  <c:v>2.3649747191744201</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>40.7451453380557</c:v>
+                  <c:v>1.6111907767763101</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>40.746132972623798</c:v>
+                  <c:v>2.3590466314134901</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>40.575608977290798</c:v>
+                  <c:v>2.11516800682289</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>44.616332334067799</c:v>
+                  <c:v>2.3666844644307399</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>44.4666727167156</c:v>
+                  <c:v>2.364144274149</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>44.613687664285798</c:v>
+                  <c:v>2.3728706942260498</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>40.736286668057403</c:v>
+                  <c:v>2.6170516776317401</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>40.763142728059599</c:v>
+                  <c:v>2.62405970857266</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>40.694432403590199</c:v>
+                  <c:v>2.6120966980614599</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>44.701040177539298</c:v>
+                  <c:v>2.36309304201417</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>40.677058071130901</c:v>
+                  <c:v>2.6201955001605399</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>44.622362690345597</c:v>
+                  <c:v>2.35928944079139</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>44.697225328150097</c:v>
+                  <c:v>2.3638347422263699</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>40.6733919444547</c:v>
+                  <c:v>2.3945236811547299</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>44.661055130400001</c:v>
+                  <c:v>2.58299659232559</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>44.6568586101967</c:v>
+                  <c:v>1.6180157872347001</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>44.628084464145999</c:v>
+                  <c:v>2.4105463237479001</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>44.632925884139702</c:v>
+                  <c:v>2.6072907634045199</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1041,6 +1038,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1048,7 +1046,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1392,6 +1389,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1399,7 +1397,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3142,16 +3139,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>319087</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>103187</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>204787</xdr:rowOff>
+      <xdr:rowOff>541337</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3484,13 +3481,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3543,7 +3540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -3607,7 +3604,7 @@
         <v>6.4376847684804355E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
@@ -3671,7 +3668,7 @@
         <v>1.0006774214028524E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
@@ -3735,7 +3732,7 @@
         <v>0.15544057489460678</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>37</v>
       </c>
@@ -3799,7 +3796,7 @@
         <v>0.74019321378384173</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -3828,7 +3825,7 @@
         <v>7.64551735307702E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -3857,7 +3854,7 @@
         <v>6.35013588849108E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -3886,7 +3883,7 @@
         <v>7.6369637116306998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -3915,7 +3912,7 @@
         <v>5.15273690367364E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
@@ -3944,7 +3941,7 @@
         <v>6.4158253499953201E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -3973,7 +3970,7 @@
         <v>6.0421286804800602E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -4002,7 +3999,7 @@
         <v>5.3269105898450997E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>45</v>
       </c>
@@ -4031,7 +4028,7 @@
         <v>6.5227108878274298E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
@@ -4060,7 +4057,7 @@
         <v>7.1620363442923898E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>47</v>
       </c>
@@ -4089,7 +4086,7 @@
         <v>5.5244350732426397E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
@@ -4118,7 +4115,7 @@
         <v>5.26355527396091E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>49</v>
       </c>
@@ -4147,7 +4144,7 @@
         <v>5.38210001880037E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>50</v>
       </c>
@@ -4176,7 +4173,7 @@
         <v>5.12051375421535E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -4205,7 +4202,7 @@
         <v>5.7838012277722801E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
@@ -4234,7 +4231,7 @@
         <v>5.3483048494557496E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>53</v>
       </c>
@@ -4263,7 +4260,7 @@
         <v>7.6207599468052804E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -4292,7 +4289,7 @@
         <v>6.46510995343616E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -4321,7 +4318,7 @@
         <v>7.6519801699284299E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>56</v>
       </c>
@@ -4350,7 +4347,7 @@
         <v>6.8838497195246699E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
@@ -4379,7 +4376,7 @@
         <v>5.17262490999593E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>58</v>
       </c>
@@ -4408,7 +4405,7 @@
         <v>5.3540400971936603E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -4437,7 +4434,7 @@
         <v>6.7613327506030399E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>60</v>
       </c>
@@ -4466,7 +4463,7 @@
         <v>7.6500069788869697E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>61</v>
       </c>
@@ -4495,7 +4492,7 @@
         <v>6.0405541735387702E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>62</v>
       </c>
@@ -4524,7 +4521,7 @@
         <v>7.6115426517561801E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>63</v>
       </c>
@@ -4553,7 +4550,7 @@
         <v>5.3812878085181997E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>64</v>
       </c>
@@ -4582,7 +4579,7 @@
         <v>7.5918069682348599E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -4611,7 +4608,7 @@
         <v>6.7632198641627396E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -4640,7 +4637,7 @@
         <v>7.1949995007469401E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>67</v>
       </c>
@@ -4678,12 +4675,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DE93493-8AF1-41A2-BECD-C23FCCD7B8BC}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4730,7 +4727,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4788,7 +4785,7 @@
       </c>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -4846,7 +4843,7 @@
       </c>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -4904,7 +4901,7 @@
       </c>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4962,7 +4959,7 @@
       </c>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -4988,7 +4985,7 @@
         <v>5.7118782522832E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -5014,7 +5011,7 @@
         <v>5.8093074214184297E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -5040,7 +5037,7 @@
         <v>5.7560434872749297E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -5066,7 +5063,7 @@
         <v>5.83142567843851E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -5092,7 +5089,7 @@
         <v>5.9052317420837198E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -5118,7 +5115,7 @@
         <v>5.84112100186851E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -5144,7 +5141,7 @@
         <v>5.9033208704615897E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -5170,7 +5167,7 @@
         <v>5.8782461248282999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -5196,7 +5193,7 @@
         <v>5.9122161900452601E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -5222,7 +5219,7 @@
         <v>5.8424956327953602E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -5248,7 +5245,7 @@
         <v>5.8634524378735502E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -5274,7 +5271,7 @@
         <v>5.9345409350320497E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -5300,7 +5297,7 @@
         <v>5.9156247281704301E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -5326,7 +5323,7 @@
         <v>5.9030370984156103E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -5352,7 +5349,7 @@
         <v>5.8694922739556503E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -5378,7 +5375,7 @@
         <v>5.8671660122002797E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -5413,9 +5410,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96149B09-0597-442B-9E81-527CD187BB1B}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5429,7 +5426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -5443,7 +5440,7 @@
         <v>11.1770115437445</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -5457,7 +5454,7 @@
         <v>11.329302054832899</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -5471,7 +5468,7 @@
         <v>11.3600930964895</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -5485,7 +5482,7 @@
         <v>11.3608067417883</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -5499,7 +5496,7 @@
         <v>11.2077787773182</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -5513,7 +5510,7 @@
         <v>11.3591768457862</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -5527,7 +5524,7 @@
         <v>11.3151694371932</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -5541,7 +5538,7 @@
         <v>11.3416526476838</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -5555,7 +5552,7 @@
         <v>11.2733188316857</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -5569,7 +5566,7 @@
         <v>11.3890419779139</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -5583,7 +5580,7 @@
         <v>11.293114778862501</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -5597,7 +5594,7 @@
         <v>11.283064557196401</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -5611,7 +5608,7 @@
         <v>11.465869859655999</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -5625,7 +5622,7 @@
         <v>11.213397155062999</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -5639,7 +5636,7 @@
         <v>11.371341530264001</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -5653,7 +5650,7 @@
         <v>11.2500539704759</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -5667,7 +5664,7 @@
         <v>11.260353899465199</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -5681,7 +5678,7 @@
         <v>11.259822883760901</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -5695,7 +5692,7 @@
         <v>11.1846809114396</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -5709,7 +5706,7 @@
         <v>11.335767756404501</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>

--- a/BeatnotePostCombFix/Apr22,2026/April22Data.xlsx
+++ b/BeatnotePostCombFix/Apr22,2026/April22Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostCombFix\Apr22,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostCombFix\Apr22,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80EFFB8-EEDC-4A03-9B70-580FC4BAD565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A532323-622A-4F34-8409-41E32B609D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36000" yWindow="2985" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="456" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -648,7 +651,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -656,6 +658,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1038,7 +1041,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1046,6 +1048,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1389,7 +1392,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1397,6 +1399,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3103,16 +3106,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>450850</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>425450</xdr:rowOff>
+      <xdr:rowOff>254000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>146050</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>403225</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>406400</xdr:rowOff>
+      <xdr:rowOff>234950</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3139,16 +3142,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>406400</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>103187</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>92075</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>112712</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>541337</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>396875</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>360362</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3481,13 +3484,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3540,7 +3543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -3604,7 +3607,7 @@
         <v>6.4376847684804355E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
@@ -3668,7 +3671,7 @@
         <v>1.0006774214028524E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
@@ -3732,7 +3735,7 @@
         <v>0.15544057489460678</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>37</v>
       </c>
@@ -3796,7 +3799,7 @@
         <v>0.74019321378384173</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -3825,7 +3828,7 @@
         <v>7.64551735307702E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -3854,7 +3857,7 @@
         <v>6.35013588849108E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -3883,7 +3886,7 @@
         <v>7.6369637116306998E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -3912,7 +3915,7 @@
         <v>5.15273690367364E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
@@ -3941,7 +3944,7 @@
         <v>6.4158253499953201E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -3970,7 +3973,7 @@
         <v>6.0421286804800602E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -3999,7 +4002,7 @@
         <v>5.3269105898450997E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>45</v>
       </c>
@@ -4028,7 +4031,7 @@
         <v>6.5227108878274298E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
@@ -4057,7 +4060,7 @@
         <v>7.1620363442923898E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>47</v>
       </c>
@@ -4086,7 +4089,7 @@
         <v>5.5244350732426397E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
@@ -4115,7 +4118,7 @@
         <v>5.26355527396091E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>49</v>
       </c>
@@ -4144,7 +4147,7 @@
         <v>5.38210001880037E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>50</v>
       </c>
@@ -4173,7 +4176,7 @@
         <v>5.12051375421535E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -4202,7 +4205,7 @@
         <v>5.7838012277722801E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
@@ -4231,7 +4234,7 @@
         <v>5.3483048494557496E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>53</v>
       </c>
@@ -4260,7 +4263,7 @@
         <v>7.6207599468052804E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -4289,7 +4292,7 @@
         <v>6.46510995343616E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -4318,7 +4321,7 @@
         <v>7.6519801699284299E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>56</v>
       </c>
@@ -4347,7 +4350,7 @@
         <v>6.8838497195246699E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>57</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>5.17262490999593E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>58</v>
       </c>
@@ -4405,7 +4408,7 @@
         <v>5.3540400971936603E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>59</v>
       </c>
@@ -4434,7 +4437,7 @@
         <v>6.7613327506030399E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>60</v>
       </c>
@@ -4463,7 +4466,7 @@
         <v>7.6500069788869697E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>61</v>
       </c>
@@ -4492,7 +4495,7 @@
         <v>6.0405541735387702E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>62</v>
       </c>
@@ -4521,7 +4524,7 @@
         <v>7.6115426517561801E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>63</v>
       </c>
@@ -4550,7 +4553,7 @@
         <v>5.3812878085181997E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>64</v>
       </c>
@@ -4579,7 +4582,7 @@
         <v>7.5918069682348599E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -4608,7 +4611,7 @@
         <v>6.7632198641627396E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
@@ -4637,7 +4640,7 @@
         <v>7.1949995007469401E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>67</v>
       </c>
@@ -4675,12 +4678,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DE93493-8AF1-41A2-BECD-C23FCCD7B8BC}">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4727,7 +4730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4785,7 +4788,7 @@
       </c>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -4843,7 +4846,7 @@
       </c>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -4901,7 +4904,7 @@
       </c>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4959,7 +4962,7 @@
       </c>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -4985,7 +4988,7 @@
         <v>5.7118782522832E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -5011,7 +5014,7 @@
         <v>5.8093074214184297E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -5037,7 +5040,7 @@
         <v>5.7560434872749297E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -5063,7 +5066,7 @@
         <v>5.83142567843851E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -5089,7 +5092,7 @@
         <v>5.9052317420837198E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -5115,7 +5118,7 @@
         <v>5.84112100186851E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -5141,7 +5144,7 @@
         <v>5.9033208704615897E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -5167,7 +5170,7 @@
         <v>5.8782461248282999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -5193,7 +5196,7 @@
         <v>5.9122161900452601E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -5219,7 +5222,7 @@
         <v>5.8424956327953602E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -5245,7 +5248,7 @@
         <v>5.8634524378735502E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -5271,7 +5274,7 @@
         <v>5.9345409350320497E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -5297,7 +5300,7 @@
         <v>5.9156247281704301E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -5323,7 +5326,7 @@
         <v>5.9030370984156103E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -5349,7 +5352,7 @@
         <v>5.8694922739556503E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -5375,7 +5378,7 @@
         <v>5.8671660122002797E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
@@ -5410,9 +5413,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96149B09-0597-442B-9E81-527CD187BB1B}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5426,7 +5429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -5440,7 +5443,7 @@
         <v>11.1770115437445</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -5454,7 +5457,7 @@
         <v>11.329302054832899</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -5468,7 +5471,7 @@
         <v>11.3600930964895</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -5482,7 +5485,7 @@
         <v>11.3608067417883</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -5496,7 +5499,7 @@
         <v>11.2077787773182</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -5510,7 +5513,7 @@
         <v>11.3591768457862</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -5524,7 +5527,7 @@
         <v>11.3151694371932</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -5538,7 +5541,7 @@
         <v>11.3416526476838</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -5552,7 +5555,7 @@
         <v>11.2733188316857</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -5566,7 +5569,7 @@
         <v>11.3890419779139</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -5580,7 +5583,7 @@
         <v>11.293114778862501</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -5594,7 +5597,7 @@
         <v>11.283064557196401</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -5608,7 +5611,7 @@
         <v>11.465869859655999</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -5622,7 +5625,7 @@
         <v>11.213397155062999</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -5636,7 +5639,7 @@
         <v>11.371341530264001</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -5650,7 +5653,7 @@
         <v>11.2500539704759</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -5664,7 +5667,7 @@
         <v>11.260353899465199</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -5678,7 +5681,7 @@
         <v>11.259822883760901</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -5692,7 +5695,7 @@
         <v>11.1846809114396</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -5706,7 +5709,7 @@
         <v>11.335767756404501</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
